--- a/data/cns_infrastructure.xlsx
+++ b/data/cns_infrastructure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFED14E3-A6A1-4B28-9EFA-456C24A205EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B153DF7-DA1C-4C6E-9EE0-061E31C13C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="navaids1" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="70">
   <si>
     <t>State</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
 </sst>
 </file>
@@ -352,8 +355,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -634,16 +639,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -673,22 +678,22 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -696,23 +701,23 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -720,45 +725,45 @@
         <v>11</v>
       </c>
       <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5">
         <v>7</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -771,40 +776,40 @@
       <c r="C6">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E7">
         <v>7</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -814,20 +819,20 @@
       <c r="B8">
         <v>5</v>
       </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -835,45 +840,45 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G9">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -883,16 +888,16 @@
       <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E11">
         <v>9</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G11">
@@ -904,22 +909,22 @@
         <v>19</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -927,22 +932,22 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13">
-        <v>2</v>
+      <c r="G13" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -952,20 +957,20 @@
       <c r="B14">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E14">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G14">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -973,22 +978,22 @@
         <v>22</v>
       </c>
       <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
+      <c r="D15">
         <v>14</v>
       </c>
-      <c r="C15">
-        <v>15</v>
-      </c>
-      <c r="D15">
-        <v>20</v>
-      </c>
       <c r="E15">
-        <v>52</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>106</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -998,20 +1003,20 @@
       <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1019,32 +1024,32 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>9</v>
+        <v>36</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D18">
@@ -1053,11 +1058,11 @@
       <c r="E18">
         <v>46</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G18">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1067,20 +1072,20 @@
       <c r="B19">
         <v>2</v>
       </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E19">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G19">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1088,12 +1093,12 @@
         <v>27</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E20">
@@ -1103,7 +1108,7 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1113,16 +1118,16 @@
       <c r="B21">
         <v>5</v>
       </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E21">
         <v>7</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G21">
@@ -1134,22 +1139,22 @@
         <v>29</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>18</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E22">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1159,10 +1164,10 @@
       <c r="B23">
         <v>3</v>
       </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E23">
@@ -1171,7 +1176,7 @@
       <c r="F23">
         <v>1</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1185,13 +1190,13 @@
       <c r="C24">
         <v>1</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E24">
         <v>4</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G24">
@@ -1202,22 +1207,22 @@
       <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
-      <c r="F25" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="F25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1225,19 +1230,19 @@
       <c r="A26" t="s">
         <v>33</v>
       </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G26">
@@ -1248,22 +1253,22 @@
       <c r="A27" t="s">
         <v>34</v>
       </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="F27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1271,22 +1276,22 @@
       <c r="A28" t="s">
         <v>35</v>
       </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1294,22 +1299,22 @@
       <c r="A29" t="s">
         <v>64</v>
       </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1323,13 +1328,13 @@
       <c r="C30">
         <v>6</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E30">
         <v>4</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G30">
@@ -1343,16 +1348,16 @@
       <c r="B31">
         <v>2</v>
       </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E31">
         <v>3</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G31">
@@ -1369,17 +1374,17 @@
       <c r="C32">
         <v>13</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E32">
         <v>31</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G32">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1387,22 +1392,22 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>17</v>
-      </c>
-      <c r="C33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E33">
-        <v>22</v>
-      </c>
-      <c r="F33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G33">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1425,7 +1430,7 @@
         <v>2</v>
       </c>
       <c r="G34">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1433,44 +1438,44 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>8</v>
-      </c>
-      <c r="C35" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E35">
-        <v>16</v>
-      </c>
-      <c r="F35" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G35">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>41</v>
       </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>9</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="B36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1478,23 +1483,23 @@
       <c r="A37" t="s">
         <v>66</v>
       </c>
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="B37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E37">
         <v>10</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G37">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1502,18 +1507,18 @@
         <v>42</v>
       </c>
       <c r="B38">
-        <v>5</v>
-      </c>
-      <c r="C38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E38">
         <v>5</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G38">
@@ -1524,23 +1529,23 @@
       <c r="A39" t="s">
         <v>43</v>
       </c>
-      <c r="B39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="B39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E39">
         <v>5</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1551,9 +1556,9 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>13</v>
-      </c>
-      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E40">
@@ -1563,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="G40">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1573,20 +1578,20 @@
       <c r="B41">
         <v>19</v>
       </c>
-      <c r="C41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E41">
         <v>23</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G41">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1594,22 +1599,22 @@
         <v>45</v>
       </c>
       <c r="B42">
-        <v>6</v>
-      </c>
-      <c r="C42" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E42">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1620,19 +1625,19 @@
         <v>5</v>
       </c>
       <c r="C43">
-        <v>24</v>
-      </c>
-      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E43">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1642,16 +1647,16 @@
       <c r="B44">
         <v>9</v>
       </c>
-      <c r="C44" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E44">
         <v>7</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G44">
@@ -1663,22 +1668,22 @@
         <v>48</v>
       </c>
       <c r="B45">
-        <v>16</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45">
-        <v>46</v>
-      </c>
-      <c r="F45" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G45">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1686,23 +1691,31 @@
         <v>49</v>
       </c>
       <c r="B46">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="C46">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D46">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E46">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="F46">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G46">
-        <v>885</v>
-      </c>
+        <v>704</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1742,13 +1755,13 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E2">
@@ -1759,7 +1772,7 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C3">
@@ -1769,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1793,7 +1806,7 @@
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C5">
@@ -1810,7 +1823,7 @@
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C6">
@@ -1820,20 +1833,20 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E7">
@@ -1844,7 +1857,7 @@
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C8">
@@ -1854,14 +1867,14 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C9">
@@ -1871,20 +1884,20 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B10">
-        <v>1</v>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E10">
@@ -1895,17 +1908,17 @@
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1929,14 +1942,14 @@
       <c r="A13" t="s">
         <v>20</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>6</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -1964,29 +1977,29 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D15">
         <v>30</v>
       </c>
       <c r="E15">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C16">
         <v>5</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E16">
@@ -1998,16 +2011,16 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E17">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2015,24 +2028,24 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
-      <c r="B19">
-        <v>4</v>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C19">
         <v>4</v>
@@ -2041,7 +2054,7 @@
         <v>4</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2083,23 +2096,23 @@
         <v>29</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C23">
@@ -2116,7 +2129,7 @@
       <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C24">
@@ -2126,14 +2139,14 @@
         <v>2</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C25">
@@ -2150,13 +2163,13 @@
       <c r="A26" t="s">
         <v>33</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E26">
@@ -2167,7 +2180,7 @@
       <c r="A27" t="s">
         <v>34</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C27">
@@ -2184,16 +2197,16 @@
       <c r="A28" t="s">
         <v>35</v>
       </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2201,16 +2214,16 @@
       <c r="A29" t="s">
         <v>64</v>
       </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2218,8 +2231,8 @@
       <c r="A30" t="s">
         <v>36</v>
       </c>
-      <c r="B30">
-        <v>8</v>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C30">
         <v>9</v>
@@ -2228,20 +2241,20 @@
         <v>7</v>
       </c>
       <c r="E30">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E31">
@@ -2253,30 +2266,30 @@
         <v>38</v>
       </c>
       <c r="B32">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C32">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>39</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E33">
         <v>15</v>
@@ -2303,7 +2316,7 @@
       <c r="A35" t="s">
         <v>40</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C35">
@@ -2320,16 +2333,16 @@
       <c r="A36" t="s">
         <v>41</v>
       </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="B36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2344,17 +2357,17 @@
         <v>4</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C38">
@@ -2371,7 +2384,7 @@
       <c r="A39" t="s">
         <v>43</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C39">
@@ -2388,8 +2401,8 @@
       <c r="A40" t="s">
         <v>67</v>
       </c>
-      <c r="B40">
-        <v>1</v>
+      <c r="B40" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C40">
         <v>48</v>
@@ -2409,7 +2422,7 @@
         <v>8</v>
       </c>
       <c r="C41">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -2422,17 +2435,17 @@
       <c r="A42" t="s">
         <v>45</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
       <c r="E42">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2440,23 +2453,23 @@
         <v>46</v>
       </c>
       <c r="B43">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C43">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D43">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E43">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>47</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C44">
@@ -2466,7 +2479,7 @@
         <v>6</v>
       </c>
       <c r="E44">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -2474,16 +2487,16 @@
         <v>48</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D45">
         <v>28</v>
       </c>
       <c r="E45">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -2491,16 +2504,16 @@
         <v>49</v>
       </c>
       <c r="B46">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C46">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="D46">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E46">
-        <v>818</v>
+        <v>812</v>
       </c>
     </row>
   </sheetData>
@@ -2510,7 +2523,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9D461FC-19FE-4B27-93E8-AC7078BCA6DD}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -2540,7 +2553,7 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C2">
@@ -2550,7 +2563,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -2580,54 +2593,54 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>9</v>
-      </c>
-      <c r="E4">
-        <v>74</v>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="B6" t="s">
+        <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6">
-        <v>2</v>
+      <c r="D6" t="s">
+        <v>9</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -2641,10 +2654,10 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>21</v>
@@ -2661,39 +2674,39 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>10</v>
+        <v>69</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
+        <v>69</v>
+      </c>
+      <c r="F8" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9">
-        <v>2</v>
+      <c r="B9" t="s">
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9">
-        <v>6</v>
+        <v>69</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9">
-        <v>3</v>
+        <v>69</v>
+      </c>
+      <c r="F9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2701,7 +2714,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
@@ -2710,7 +2723,7 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -2720,20 +2733,20 @@
       <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11">
-        <v>32</v>
-      </c>
-      <c r="F11">
-        <v>22</v>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2741,19 +2754,19 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12">
-        <v>26</v>
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2761,19 +2774,19 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13">
-        <v>117</v>
+        <v>69</v>
+      </c>
+      <c r="E13" t="s">
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2781,19 +2794,19 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E14">
         <v>17</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2809,8 +2822,8 @@
       <c r="D15">
         <v>4</v>
       </c>
-      <c r="E15">
-        <v>31</v>
+      <c r="E15" t="s">
+        <v>9</v>
       </c>
       <c r="F15">
         <v>7</v>
@@ -2820,20 +2833,20 @@
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>21</v>
-      </c>
-      <c r="C16">
-        <v>15</v>
-      </c>
-      <c r="D16">
-        <v>57</v>
-      </c>
-      <c r="E16">
-        <v>37</v>
-      </c>
-      <c r="F16">
-        <v>14</v>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2849,8 +2862,8 @@
       <c r="D17" t="s">
         <v>9</v>
       </c>
-      <c r="E17" t="s">
-        <v>9</v>
+      <c r="E17">
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -2860,20 +2873,20 @@
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>4</v>
+      <c r="B18" t="s">
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18">
-        <v>12</v>
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18">
-        <v>4</v>
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2901,13 +2914,13 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -2920,40 +2933,40 @@
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>25</v>
+      <c r="B21" t="s">
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21">
-        <v>48</v>
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22">
-        <v>1</v>
+      <c r="B22" t="s">
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22">
-        <v>6</v>
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2969,8 +2982,8 @@
       <c r="D23">
         <v>7</v>
       </c>
-      <c r="E23">
-        <v>30</v>
+      <c r="E23" t="s">
+        <v>9</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
@@ -2989,8 +3002,8 @@
       <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24" t="s">
-        <v>9</v>
+      <c r="E24">
+        <v>4</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
@@ -3009,8 +3022,8 @@
       <c r="D25">
         <v>3</v>
       </c>
-      <c r="E25">
-        <v>4</v>
+      <c r="E25" t="s">
+        <v>9</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -3020,20 +3033,20 @@
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
+        <v>69</v>
+      </c>
+      <c r="F26" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -3049,8 +3062,8 @@
       <c r="D27">
         <v>1</v>
       </c>
-      <c r="E27">
-        <v>15</v>
+      <c r="E27" t="s">
+        <v>9</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
@@ -3067,10 +3080,10 @@
         <v>1</v>
       </c>
       <c r="D28">
-        <v>10</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E28">
+        <v>61</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
@@ -3078,286 +3091,312 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29">
-        <v>6</v>
-      </c>
-      <c r="C29">
-        <v>12</v>
-      </c>
-      <c r="D29">
-        <v>13</v>
+        <v>37</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29">
-        <v>12</v>
+        <v>69</v>
+      </c>
+      <c r="F29" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30">
-        <v>4</v>
-      </c>
-      <c r="C30">
-        <v>4</v>
-      </c>
-      <c r="D30">
-        <v>20</v>
-      </c>
-      <c r="E30">
-        <v>180</v>
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" t="s">
+        <v>69</v>
       </c>
       <c r="F30" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E31">
-        <v>10</v>
-      </c>
-      <c r="F31">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-      <c r="D32">
-        <v>9</v>
-      </c>
-      <c r="E32">
-        <v>60</v>
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" t="s">
+        <v>69</v>
       </c>
       <c r="F32" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33">
-        <v>5</v>
-      </c>
-      <c r="E33">
-        <v>43</v>
+        <v>69</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" t="s">
+        <v>69</v>
       </c>
       <c r="F33" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34">
-        <v>2</v>
+        <v>51</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
       </c>
-      <c r="F34">
-        <v>3</v>
+      <c r="F34" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35">
-        <v>2</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
-      <c r="F35" t="s">
-        <v>9</v>
+      <c r="F35">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36">
-        <v>12</v>
-      </c>
-      <c r="C36">
-        <v>9</v>
-      </c>
-      <c r="D36">
-        <v>40</v>
-      </c>
-      <c r="E36">
-        <v>36</v>
-      </c>
-      <c r="F36">
-        <v>35</v>
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
-        <v>4</v>
-      </c>
-      <c r="D37">
-        <v>12</v>
-      </c>
-      <c r="E37">
-        <v>2</v>
+        <v>50</v>
+      </c>
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" t="s">
+        <v>69</v>
       </c>
       <c r="F37" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="B38" t="s">
+        <v>69</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38">
-        <v>15</v>
+        <v>69</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="F38" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" t="s">
-        <v>9</v>
+        <v>45</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
       </c>
       <c r="D39">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E39">
-        <v>37</v>
-      </c>
-      <c r="F39">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="F39" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
       </c>
-      <c r="C40">
+      <c r="C40" t="s">
         <v>9</v>
       </c>
       <c r="D40">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41">
-        <v>13</v>
-      </c>
-      <c r="C41">
-        <v>3</v>
-      </c>
-      <c r="D41">
-        <v>58</v>
-      </c>
-      <c r="E41">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="B41" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" t="s">
+        <v>69</v>
       </c>
       <c r="F41" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42">
+        <v>22</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42">
+        <v>57</v>
+      </c>
+      <c r="E42">
+        <v>51</v>
+      </c>
+      <c r="F42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>68</v>
       </c>
-      <c r="B42">
-        <v>142</v>
-      </c>
-      <c r="C42">
-        <v>139</v>
-      </c>
-      <c r="D42">
-        <v>526</v>
-      </c>
-      <c r="E42">
-        <v>908</v>
-      </c>
-      <c r="F42">
-        <v>155</v>
+      <c r="B43">
+        <v>148</v>
+      </c>
+      <c r="C43">
+        <v>117</v>
+      </c>
+      <c r="D43">
+        <v>581</v>
+      </c>
+      <c r="E43">
+        <v>1087</v>
+      </c>
+      <c r="F43">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>